--- a/input_data/demo_model.xlsx
+++ b/input_data/demo_model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsdennis\HOPE\Predicer\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B29F9F6-B68D-44BC-94AB-B3530B6CDFDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{126EFFD4-1C7C-44ED-B784-97D3C87E86E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="796" activeTab="1" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="796" firstSheet="7" activeTab="14" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
   </bookViews>
   <sheets>
     <sheet name="timeseries" sheetId="18" r:id="rId1"/>
@@ -27,20 +27,21 @@
     <sheet name="cf" sheetId="7" r:id="rId12"/>
     <sheet name="inflow" sheetId="3" r:id="rId13"/>
     <sheet name="inflow_blocks" sheetId="22" r:id="rId14"/>
-    <sheet name="price" sheetId="4" r:id="rId15"/>
-    <sheet name="markets" sheetId="5" r:id="rId16"/>
-    <sheet name="bid_slots" sheetId="29" r:id="rId17"/>
-    <sheet name="reserve_realisation" sheetId="23" r:id="rId18"/>
-    <sheet name="market_prices" sheetId="8" r:id="rId19"/>
-    <sheet name="balance_prices" sheetId="20" r:id="rId20"/>
-    <sheet name="reserve_activation_price" sheetId="28" r:id="rId21"/>
-    <sheet name="risk" sheetId="17" r:id="rId22"/>
-    <sheet name="scenarios" sheetId="9" r:id="rId23"/>
-    <sheet name="fixed_ts" sheetId="11" r:id="rId24"/>
-    <sheet name="eff_ts" sheetId="12" r:id="rId25"/>
-    <sheet name="cap_ts" sheetId="16" r:id="rId26"/>
-    <sheet name="constraints" sheetId="14" r:id="rId27"/>
-    <sheet name="gen_constraint" sheetId="15" r:id="rId28"/>
+    <sheet name="flex_inflow" sheetId="30" r:id="rId15"/>
+    <sheet name="price" sheetId="4" r:id="rId16"/>
+    <sheet name="markets" sheetId="5" r:id="rId17"/>
+    <sheet name="bid_slots" sheetId="29" r:id="rId18"/>
+    <sheet name="reserve_realisation" sheetId="23" r:id="rId19"/>
+    <sheet name="market_prices" sheetId="8" r:id="rId20"/>
+    <sheet name="balance_prices" sheetId="20" r:id="rId21"/>
+    <sheet name="reserve_activation_price" sheetId="28" r:id="rId22"/>
+    <sheet name="risk" sheetId="17" r:id="rId23"/>
+    <sheet name="scenarios" sheetId="9" r:id="rId24"/>
+    <sheet name="fixed_ts" sheetId="11" r:id="rId25"/>
+    <sheet name="eff_ts" sheetId="12" r:id="rId26"/>
+    <sheet name="cap_ts" sheetId="16" r:id="rId27"/>
+    <sheet name="constraints" sheetId="14" r:id="rId28"/>
+    <sheet name="gen_constraint" sheetId="15" r:id="rId29"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="131">
   <si>
     <t>node</t>
   </si>
@@ -438,6 +439,21 @@
   </si>
   <si>
     <t>common_end_timesteps</t>
+  </si>
+  <si>
+    <t>period_name</t>
+  </si>
+  <si>
+    <t>scenario</t>
+  </si>
+  <si>
+    <t>t_start</t>
+  </si>
+  <si>
+    <t>t_end</t>
+  </si>
+  <si>
+    <t>inflow</t>
   </si>
 </sst>
 </file>
@@ -490,13 +506,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4658,9 +4671,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4698,7 +4711,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -4804,7 +4817,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4946,7 +4959,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4955,179 +4968,179 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39053E69-3A75-490E-847C-66A9CF6C1FC5}">
   <dimension ref="A1:A49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <v>44671.208333043978</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <v>44671.249999537038</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <v>44671.291666087964</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <v>44671.333332638889</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <v>44671.374999189815</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="8"/>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="8"/>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="8"/>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="8"/>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="8"/>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="8"/>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="8"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="8"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="8"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="8"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="8"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="8"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="8"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="8"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="8"/>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="8"/>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="8"/>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="8"/>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="8"/>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="8"/>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="8"/>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="8"/>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="8"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="8"/>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5"/>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5"/>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5"/>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="5"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="5"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="5"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="5"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="5"/>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="5"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="5"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="5"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="5"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="5"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="5"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="5"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="5"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="5"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="5"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" s="5"/>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" s="5"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" s="5"/>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" s="5"/>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" s="5"/>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" s="5"/>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" s="5"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5138,74 +5151,74 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E3CA5E7-5C31-4336-93EE-0293D708EE58}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
@@ -5219,13 +5232,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0532F8A-0FB4-47AD-98A1-4065D3376432}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>39</v>
       </c>
     </row>
@@ -5237,30 +5250,30 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77A4637A-7829-48D6-AE54-2E654AB1A427}">
   <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
-    <col min="2" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+    <col min="2" max="5" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
@@ -5273,11 +5286,11 @@
       <c r="D2">
         <v>0.25</v>
       </c>
-      <c r="F2" s="8"/>
-      <c r="L2" s="8"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+      <c r="F2" s="5"/>
+      <c r="L2" s="5"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -5291,8 +5304,8 @@
         <v>0.34899999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -5306,8 +5319,8 @@
         <v>0.27899999999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
@@ -5321,8 +5334,8 @@
         <v>0.36299999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
@@ -5336,8 +5349,8 @@
         <v>0.27600000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
@@ -5351,8 +5364,8 @@
         <v>0.23500000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
@@ -5366,8 +5379,8 @@
         <v>0.17500000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
@@ -5381,8 +5394,8 @@
         <v>0.17600000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
@@ -5396,8 +5409,8 @@
         <v>0.21400000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
@@ -5411,86 +5424,86 @@
         <v>0.27400000000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="str">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="str">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="str">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="str">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="str">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -5506,29 +5519,29 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F87DD44-A1AD-4241-AED7-C48CC9DEE2E2}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
-    <col min="4" max="6" width="10.42578125" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+    <col min="4" max="6" width="10.44140625" customWidth="1"/>
+    <col min="7" max="7" width="10.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
@@ -5541,11 +5554,10 @@
       <c r="D2">
         <v>-7.84</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+      <c r="G2"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -5558,11 +5570,10 @@
       <c r="D3">
         <v>-7.07</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+      <c r="G3"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -5575,11 +5586,10 @@
       <c r="D4">
         <v>-6.73</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+      <c r="G4"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
@@ -5592,11 +5602,10 @@
       <c r="D5">
         <v>-6.65</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+      <c r="G5"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
@@ -5609,11 +5618,10 @@
       <c r="D6">
         <v>-7.08</v>
       </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+      <c r="G6"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
@@ -5626,11 +5634,10 @@
       <c r="D7">
         <v>-6.79</v>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+      <c r="G7"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
@@ -5643,11 +5650,10 @@
       <c r="D8">
         <v>-7.13</v>
       </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+      <c r="G8"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
@@ -5660,11 +5666,10 @@
       <c r="D9">
         <v>-7.41</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+      <c r="G9"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
@@ -5677,11 +5682,10 @@
       <c r="D10">
         <v>-7.2700000000000005</v>
       </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+      <c r="G10"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
@@ -5694,120 +5698,105 @@
       <c r="D11">
         <v>-7.7</v>
       </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="str">
+      <c r="G11"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="str">
+      <c r="G12"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="str">
+      <c r="G13"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="str">
+      <c r="G14"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="str">
+      <c r="G15"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="str">
+      <c r="G16"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="str">
+      <c r="G17"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="str">
+      <c r="G18"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="str">
+      <c r="G19"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="str">
+      <c r="G20"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="str">
+      <c r="G21"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="str">
+      <c r="G22"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="str">
+      <c r="G23"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="str">
+      <c r="G24"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
+      <c r="G25"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5820,86 +5809,86 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E44A96C9-CA4B-4735-AF1E-65BD86DB3657}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" customWidth="1"/>
+    <col min="3" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="E2" s="8"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C2" s="5"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="E3" s="8"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C3" s="5"/>
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="E4" s="8"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C4" s="5"/>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="E5" s="8"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C5" s="5"/>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-    </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+    </row>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5907,23 +5896,57 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{076D8023-527F-4386-8A27-2EF08439356E}">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02307C1F-427B-487D-B703-EBF512D7AC27}">
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
@@ -5931,8 +5954,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -5940,8 +5963,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -5949,8 +5972,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
@@ -5958,8 +5981,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
@@ -5967,8 +5990,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
@@ -5976,8 +5999,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
@@ -5985,8 +6008,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
@@ -5994,8 +6017,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
@@ -6003,8 +6026,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
@@ -6012,86 +6035,86 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="str">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="str">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="str">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="str">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="str">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -6102,183 +6125,105 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3788A93-7501-4F5D-9E8F-38D329CC85EC}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="7"/>
+    <col min="1" max="1" width="11" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.109375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="7">
-        <v>0</v>
-      </c>
-      <c r="G2" s="7" t="s">
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="4">
         <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2" s="7">
-        <v>0</v>
-      </c>
-      <c r="K2" s="7">
-        <v>0</v>
-      </c>
-      <c r="L2" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="I3"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="I4"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="I5"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC41313E-0921-4847-B147-12B3359B7405}">
-  <dimension ref="A1:A11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
-        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
-        <v>44671</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
-        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
-        <v>44671.041666666664</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
-        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
-        <v>44671.08333321759</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
-        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
-        <v>44671.124999826388</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
-        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
-        <v>44671.166666435187</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
-        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
-        <v>44671.208333043978</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
-        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
-        <v>44671.249999537038</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
-        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
-        <v>44671.291666087964</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
-        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
-        <v>44671.333332638889</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
-        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
-        <v>44671.374999189815</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6286,161 +6231,76 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E266E0-7523-413E-8B0C-F3E2413808A5}">
-  <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC41313E-0921-4847-B147-12B3359B7405}">
+  <dimension ref="A1:A11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
-    <col min="2" max="3" width="6.5703125" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="str">
-        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="str">
-        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="str">
-        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="str">
-        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="str">
-        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="str">
-        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="str">
-        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="str">
-        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="str">
-        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="str">
-        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="str">
-        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="str">
-        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="str">
-        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="str">
-        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -6449,31 +6309,294 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E266E0-7523-413E-8B0C-F3E2413808A5}">
+  <dimension ref="A1:A25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+    <col min="2" max="3" width="6.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
+        <v>44671</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
+        <v>44671.041666666664</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
+        <v>44671.08333321759</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
+        <v>44671.124999826388</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
+        <v>44671.166666435187</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
+        <v>44671.208333043978</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
+        <v>44671.249999537038</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
+        <v>44671.291666087964</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
+        <v>44671.333332638889</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
+        <v>44671.374999189815</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="str">
+        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="str">
+        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="str">
+        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="str">
+        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="str">
+        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="str">
+        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="str">
+        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="str">
+        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="str">
+        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="str">
+        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="str">
+        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="str">
+        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="str">
+        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="str">
+        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB98B755-8BE1-4837-9877-4DDB59C80C3F}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B7">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B8">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF6DDD9A-EF34-4108-8532-230729E9C708}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
-    <col min="2" max="6" width="11.42578125" customWidth="1"/>
-    <col min="7" max="14" width="11.140625" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+    <col min="2" max="6" width="11.44140625" customWidth="1"/>
+    <col min="7" max="14" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
@@ -6487,8 +6610,8 @@
         <v>8.98</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -6502,8 +6625,8 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -6517,8 +6640,8 @@
         <v>25.19</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
@@ -6532,8 +6655,8 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
@@ -6547,8 +6670,8 @@
         <v>25.81</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
@@ -6562,8 +6685,8 @@
         <v>23.67</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
@@ -6577,8 +6700,8 @@
         <v>50.43</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
@@ -6592,8 +6715,8 @@
         <v>36.69</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
@@ -6607,8 +6730,8 @@
         <v>6.36</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
@@ -6630,143 +6753,43 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB98B755-8BE1-4837-9877-4DDB59C80C3F}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817FDE8F-BC70-48D0-8376-FB52E6946AF1}">
+  <dimension ref="A1:H25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" customWidth="1"/>
+    <col min="5" max="6" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>111</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>118</v>
-      </c>
-      <c r="B7">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>119</v>
-      </c>
-      <c r="B8">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>124</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>125</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>113</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817FDE8F-BC70-48D0-8376-FB52E6946AF1}">
-  <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" customWidth="1"/>
-    <col min="5" max="6" width="10.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="H1" s="3"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
@@ -6795,8 +6818,8 @@
         <v>8.5310000000000006</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -6825,8 +6848,8 @@
         <v>4.2560000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -6855,8 +6878,8 @@
         <v>23.930499999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
@@ -6885,8 +6908,8 @@
         <v>18.145</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
@@ -6915,8 +6938,8 @@
         <v>24.519499999999997</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
@@ -6945,8 +6968,8 @@
         <v>22.486499999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
@@ -6975,8 +6998,8 @@
         <v>47.908499999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
@@ -7005,8 +7028,8 @@
         <v>34.855499999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
@@ -7035,8 +7058,8 @@
         <v>6.0419999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
@@ -7065,52 +7088,52 @@
         <v>14.1455</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8"/>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="5"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="5"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="5"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="5"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7118,16 +7141,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A93E100-F2EF-4A65-A77F-7D1B321EA2D7}">
   <dimension ref="A1:BA25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:53" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B1"/>
@@ -7183,185 +7206,148 @@
       <c r="AZ1"/>
       <c r="BA1"/>
     </row>
-    <row r="2" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="6" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
     </row>
-    <row r="8" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
     </row>
-    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
     </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
     </row>
-    <row r="11" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
     </row>
-    <row r="12" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="str">
+    <row r="12" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="str">
+    <row r="13" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="str">
+    <row r="14" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="str">
+    <row r="15" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="str">
+    <row r="16" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9314D326-256A-435C-AAE3-3517FA836EAE}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7370,40 +7356,35 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A87AD413-E614-48C1-80E1-F1E8236FCBC6}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9314D326-256A-435C-AAE3-3517FA836EAE}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="B2">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B3">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B4">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7412,167 +7393,40 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31679CA5-0AA2-4F6F-8223-14BF74917F04}">
-  <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A87AD413-E614-48C1-80E1-F1E8236FCBC6}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
-        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
-        <v>44671</v>
-      </c>
-      <c r="B2" s="2"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
-        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
-        <v>44671.041666666664</v>
-      </c>
-      <c r="B3" s="2"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
-        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
-        <v>44671.08333321759</v>
-      </c>
-      <c r="B4" s="2"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
-        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
-        <v>44671.124999826388</v>
-      </c>
-      <c r="B5" s="2"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
-        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
-        <v>44671.166666435187</v>
-      </c>
-      <c r="B6" s="2"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
-        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
-        <v>44671.208333043978</v>
-      </c>
-      <c r="B7" s="2"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
-        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
-        <v>44671.249999537038</v>
-      </c>
-      <c r="B8" s="2"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
-        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
-        <v>44671.291666087964</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
-        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
-        <v>44671.333332638889</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
-        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
-        <v>44671.374999189815</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="str">
-        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="str">
-        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="str">
-        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="str">
-        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="str">
-        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="str">
-        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="str">
-        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="str">
-        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="str">
-        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="str">
-        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="str">
-        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="str">
-        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="str">
-        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="str">
-        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
-        <v/>
+    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -7581,158 +7435,320 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31679CA5-0AA2-4F6F-8223-14BF74917F04}">
+  <dimension ref="A1:A25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
+        <v>44671</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
+        <v>44671.041666666664</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
+        <v>44671.08333321759</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
+        <v>44671.124999826388</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
+        <v>44671.166666435187</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
+        <v>44671.208333043978</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
+        <v>44671.249999537038</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
+        <v>44671.291666087964</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
+        <v>44671.333332638889</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
+        <v>44671.374999189815</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="str">
+        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="str">
+        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="str">
+        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="str">
+        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="str">
+        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="str">
+        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="str">
+        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="str">
+        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="str">
+        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="str">
+        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="str">
+        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="str">
+        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="str">
+        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="str">
+        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD670E02-665B-45B8-BC4E-9596D2C1BC55}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="str">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="str">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="str">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="str">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="str">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -7743,159 +7759,159 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7FEDBA5-B0F3-4E9D-9367-08D5F5FA8AEA}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="str">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="str">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="str">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="str">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="str">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -7905,17 +7921,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5704FC51-737E-45F9-9A9E-85A96AFE5439}">
   <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>31</v>
       </c>
@@ -7929,7 +7945,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -7943,10 +7959,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7954,21 +7970,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE12AB76-2BDA-4ACA-A128-8CFB9FB6C8F8}">
   <dimension ref="A1:J25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
-    <col min="2" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+    <col min="2" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B1" t="s">
@@ -7999,8 +8015,8 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
@@ -8032,8 +8048,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -8065,8 +8081,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -8098,8 +8114,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
@@ -8131,8 +8147,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
@@ -8164,8 +8180,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
@@ -8197,8 +8213,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
@@ -8230,8 +8246,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
@@ -8263,8 +8279,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
@@ -8296,8 +8312,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
@@ -8329,86 +8345,86 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="str">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="str">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="str">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="str">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="str">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -8421,287 +8437,287 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04A1B16B-CDA9-46BD-BA51-731AA9327652}">
   <dimension ref="A1:Q6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="4">
         <v>1</v>
       </c>
-      <c r="C2" s="7">
-        <v>0</v>
-      </c>
-      <c r="D2" s="7">
-        <v>0</v>
-      </c>
-      <c r="E2" s="7">
-        <v>0</v>
-      </c>
-      <c r="F2" s="7">
-        <v>0</v>
-      </c>
-      <c r="G2" s="7">
-        <v>0</v>
-      </c>
-      <c r="H2" s="7">
-        <v>0</v>
-      </c>
-      <c r="I2" s="7">
-        <v>0</v>
-      </c>
-      <c r="J2" s="7">
-        <v>0</v>
-      </c>
-      <c r="K2" s="7">
-        <v>0</v>
-      </c>
-      <c r="L2" s="7">
-        <v>0</v>
-      </c>
-      <c r="M2" s="7">
-        <v>0</v>
-      </c>
-      <c r="N2" s="7">
-        <v>0</v>
-      </c>
-      <c r="O2" s="7">
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4">
         <v>1</v>
       </c>
-      <c r="P2" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="7">
-        <v>0</v>
-      </c>
-      <c r="C3" s="7">
-        <v>0</v>
-      </c>
-      <c r="D3" s="7">
-        <v>0</v>
-      </c>
-      <c r="E3" s="7">
-        <v>0</v>
-      </c>
-      <c r="F3" s="7">
-        <v>0</v>
-      </c>
-      <c r="G3" s="7">
-        <v>0</v>
-      </c>
-      <c r="H3" s="7">
-        <v>0</v>
-      </c>
-      <c r="I3" s="7">
-        <v>0</v>
-      </c>
-      <c r="J3" s="7">
-        <v>0</v>
-      </c>
-      <c r="K3" s="7">
-        <v>0</v>
-      </c>
-      <c r="L3" s="7">
-        <v>0</v>
-      </c>
-      <c r="M3" s="7">
-        <v>0</v>
-      </c>
-      <c r="N3" s="7">
-        <v>0</v>
-      </c>
-      <c r="O3" s="7">
+      <c r="B3" s="4">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4">
         <v>1</v>
       </c>
-      <c r="P3" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>86</v>
       </c>
-      <c r="B4" s="7">
-        <v>0</v>
-      </c>
-      <c r="C4" s="7">
+      <c r="B4" s="4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4">
         <v>1</v>
       </c>
-      <c r="D4" s="7">
-        <v>0</v>
-      </c>
-      <c r="E4" s="7">
-        <v>0</v>
-      </c>
-      <c r="F4" s="7">
-        <v>0</v>
-      </c>
-      <c r="G4" s="7">
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4">
         <v>10</v>
       </c>
-      <c r="H4" s="7">
-        <v>0</v>
-      </c>
-      <c r="I4" s="7">
+      <c r="H4" s="4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
         <v>3</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="4">
         <v>3</v>
       </c>
-      <c r="K4" s="7">
-        <v>0</v>
-      </c>
-      <c r="L4" s="7">
+      <c r="K4" s="4">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
         <v>0.01</v>
       </c>
-      <c r="M4" s="7">
-        <v>0</v>
-      </c>
-      <c r="N4" s="7">
-        <v>0</v>
-      </c>
-      <c r="O4" s="7">
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4">
         <v>1</v>
       </c>
-      <c r="P4" s="7">
+      <c r="P4" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="7">
-        <v>0</v>
-      </c>
-      <c r="C5" s="7">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7">
-        <v>0</v>
-      </c>
-      <c r="E5" s="7">
-        <v>0</v>
-      </c>
-      <c r="F5" s="7">
+      <c r="B5" s="4">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4">
         <v>1</v>
       </c>
-      <c r="G5" s="7">
-        <v>0</v>
-      </c>
-      <c r="H5" s="7">
-        <v>0</v>
-      </c>
-      <c r="I5" s="7">
-        <v>0</v>
-      </c>
-      <c r="J5" s="7">
-        <v>0</v>
-      </c>
-      <c r="K5" s="7">
-        <v>0</v>
-      </c>
-      <c r="L5" s="7">
-        <v>0</v>
-      </c>
-      <c r="M5" s="7">
-        <v>0</v>
-      </c>
-      <c r="N5" s="7">
-        <v>0</v>
-      </c>
-      <c r="O5" s="7">
+      <c r="G5" s="4">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4">
         <v>1</v>
       </c>
-      <c r="P5" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
+      <c r="P5" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8711,337 +8727,337 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB20090B-02A9-43B7-8D03-9C18D42920EB}">
   <dimension ref="A1:Q6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" customWidth="1"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="11.42578125" customWidth="1"/>
-    <col min="16" max="16" width="9.140625" style="3"/>
+    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="11.44140625" customWidth="1"/>
+    <col min="16" max="16" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="7">
-        <v>0</v>
-      </c>
-      <c r="C2" s="7">
-        <v>0</v>
-      </c>
-      <c r="D2" s="7">
+      <c r="B2" s="4">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
         <v>1</v>
       </c>
-      <c r="E2" s="7">
-        <v>0</v>
-      </c>
-      <c r="F2" s="7">
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
         <v>1</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="4">
         <v>0.8</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="4">
         <v>0.4</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="4">
         <v>1</v>
       </c>
-      <c r="J2" s="7">
-        <v>0</v>
-      </c>
-      <c r="K2" s="7">
-        <v>0</v>
-      </c>
-      <c r="L2" s="7">
-        <v>0</v>
-      </c>
-      <c r="M2" s="7">
-        <v>0</v>
-      </c>
-      <c r="N2" s="7">
-        <v>0</v>
-      </c>
-      <c r="O2" s="7">
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4">
         <v>1</v>
       </c>
-      <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="4">
         <v>1</v>
       </c>
-      <c r="C3" s="7">
-        <v>0</v>
-      </c>
-      <c r="D3" s="7">
-        <v>0</v>
-      </c>
-      <c r="E3" s="7">
-        <v>0</v>
-      </c>
-      <c r="F3" s="7">
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
         <v>1</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="4">
         <v>1</v>
       </c>
-      <c r="H3" s="7">
-        <v>0</v>
-      </c>
-      <c r="I3" s="7">
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
         <v>1</v>
       </c>
-      <c r="J3" s="7">
-        <v>0</v>
-      </c>
-      <c r="K3" s="7">
-        <v>0</v>
-      </c>
-      <c r="L3" s="7">
-        <v>0</v>
-      </c>
-      <c r="M3" s="7">
-        <v>0</v>
-      </c>
-      <c r="N3" s="7">
-        <v>0</v>
-      </c>
-      <c r="O3" s="7">
-        <v>0</v>
-      </c>
-      <c r="P3" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="J3" s="4">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="7">
-        <v>0</v>
-      </c>
-      <c r="C4" s="7">
-        <v>0</v>
-      </c>
-      <c r="D4" s="7">
-        <v>0</v>
-      </c>
-      <c r="E4" s="7">
-        <v>0</v>
-      </c>
-      <c r="F4" s="7">
+      <c r="B4" s="4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
         <v>1</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="4">
         <v>3</v>
       </c>
-      <c r="H4" s="7">
-        <v>0</v>
-      </c>
-      <c r="I4" s="7">
+      <c r="H4" s="4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
         <v>1</v>
       </c>
-      <c r="J4" s="7">
-        <v>0</v>
-      </c>
-      <c r="K4" s="7">
-        <v>0</v>
-      </c>
-      <c r="L4" s="7">
-        <v>0</v>
-      </c>
-      <c r="M4" s="7">
-        <v>0</v>
-      </c>
-      <c r="N4" s="7">
-        <v>0</v>
-      </c>
-      <c r="O4" s="7">
-        <v>0</v>
-      </c>
-      <c r="P4" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="J4" s="4">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>87</v>
       </c>
-      <c r="B5" s="7">
-        <v>0</v>
-      </c>
-      <c r="C5" s="7">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7">
+      <c r="B5" s="4">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
         <v>1</v>
       </c>
-      <c r="E5" s="7">
-        <v>0</v>
-      </c>
-      <c r="F5" s="7">
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4">
         <v>1</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="4">
         <v>0.99</v>
       </c>
-      <c r="H5" s="7">
-        <v>0</v>
-      </c>
-      <c r="I5" s="7">
+      <c r="H5" s="4">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
         <v>1</v>
       </c>
-      <c r="J5" s="7">
-        <v>0</v>
-      </c>
-      <c r="K5" s="7">
-        <v>0</v>
-      </c>
-      <c r="L5" s="7">
-        <v>0</v>
-      </c>
-      <c r="M5" s="7">
-        <v>0</v>
-      </c>
-      <c r="N5" s="7">
-        <v>0</v>
-      </c>
-      <c r="O5" s="7">
-        <v>0</v>
-      </c>
-      <c r="P5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="J5" s="4">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>88</v>
       </c>
-      <c r="B6" s="7">
-        <v>0</v>
-      </c>
-      <c r="C6" s="7">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7">
+      <c r="B6" s="4">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
         <v>1</v>
       </c>
-      <c r="E6" s="7">
-        <v>0</v>
-      </c>
-      <c r="F6" s="7">
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4">
         <v>1</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="4">
         <v>0.99</v>
       </c>
-      <c r="H6" s="7">
-        <v>0</v>
-      </c>
-      <c r="I6" s="7">
+      <c r="H6" s="4">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4">
         <v>1</v>
       </c>
-      <c r="J6" s="7">
-        <v>0</v>
-      </c>
-      <c r="K6" s="7">
-        <v>0</v>
-      </c>
-      <c r="L6" s="7">
-        <v>0</v>
-      </c>
-      <c r="M6" s="7">
-        <v>0</v>
-      </c>
-      <c r="N6" s="7">
-        <v>0</v>
-      </c>
-      <c r="O6" s="7">
-        <v>0</v>
-      </c>
-      <c r="P6" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="7">
+      <c r="J6" s="4">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4">
         <v>0</v>
       </c>
     </row>
@@ -9053,20 +9069,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5539A729-4FB7-440D-A765-676495DE3453}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -9077,7 +9093,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -9088,7 +9104,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -9099,7 +9115,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -9110,7 +9126,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -9129,48 +9145,48 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAB1106B-D567-41FC-8E91-2B4CC5EC9B59}">
   <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="3">
+      <c r="B1" s="2">
         <v>1</v>
       </c>
-      <c r="C1" s="3">
+      <c r="C1" s="2">
         <f>B1+1</f>
         <v>2</v>
       </c>
-      <c r="D1" s="3">
+      <c r="D1" s="2">
         <f t="shared" ref="D1:K1" si="0">C1+1</f>
         <v>3</v>
       </c>
-      <c r="E1" s="3">
+      <c r="E1" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F1" s="3">
+      <c r="F1" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G1" s="3">
+      <c r="G1" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="H1" s="3">
+      <c r="H1" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="I1" s="3">
+      <c r="I1" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="J1" s="3">
+      <c r="J1" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K1" s="3">
+      <c r="K1" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -9183,368 +9199,367 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A86A8A7-FD76-4891-A53C-CBB095359118}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="5"/>
+    <col min="1" max="1" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2">
         <v>10</v>
       </c>
-      <c r="F2" s="5">
-        <v>0</v>
-      </c>
-      <c r="G2" s="5">
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
         <v>3</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2">
         <v>3</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2">
         <v>0.7</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2">
         <v>0.7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3">
         <v>3</v>
       </c>
-      <c r="F3" s="5">
-        <v>0</v>
-      </c>
-      <c r="G3" s="5">
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>3</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3">
         <v>3</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3">
         <v>0.7</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3">
         <v>0.7</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4">
         <v>6</v>
       </c>
-      <c r="F4" s="5">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
         <v>3</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4">
         <v>3</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4">
         <v>0.7</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4">
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5">
         <v>5</v>
       </c>
-      <c r="F5" s="5">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5">
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5">
         <v>1</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5">
         <v>0.7</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5">
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6">
         <v>1</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6">
         <v>3</v>
       </c>
-      <c r="F6" s="5">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5">
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
         <v>5</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6">
         <v>5</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6">
         <v>0.7</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6">
         <v>0.7</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7">
         <v>1</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7">
         <v>9</v>
       </c>
-      <c r="F7" s="5">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5">
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
         <v>5</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7">
         <v>5</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7">
         <v>0.7</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7">
         <v>0.7</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>87</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8">
         <v>1</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8">
         <v>3</v>
       </c>
-      <c r="F8" s="5">
-        <v>0</v>
-      </c>
-      <c r="G8" s="5">
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
         <v>15</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8">
         <v>15</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8">
         <v>0.7</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8">
         <v>0.7</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>87</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9">
         <v>1</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9">
         <v>3</v>
       </c>
-      <c r="F9" s="5">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5">
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
         <v>15</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9">
         <v>15</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9">
         <v>0.7</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9">
         <v>0.7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>88</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10">
         <v>1</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10">
         <v>3</v>
       </c>
-      <c r="F10" s="5">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5">
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
         <v>15</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10">
         <v>15</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10">
         <v>0.7</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10">
         <v>0.7</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>88</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" t="s">
         <v>86</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11">
         <v>1</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11">
         <v>3</v>
       </c>
-      <c r="F11" s="5">
-        <v>0</v>
-      </c>
-      <c r="G11" s="5">
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
         <v>15</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11">
         <v>15</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11">
         <v>0.7</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11">
         <v>0.7</v>
       </c>
     </row>
@@ -9557,156 +9572,156 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7AEF404-3743-47D7-AC45-7AE3A9FB796E}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="str">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="str">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="str">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="str">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="str">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -9719,27 +9734,27 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7B98CF0-A261-4D3A-B414-AE3BDF1136D0}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>105</v>
       </c>
     </row>

--- a/input_data/demo_model.xlsx
+++ b/input_data/demo_model.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsdennis\HOPE\Predicer\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{126EFFD4-1C7C-44ED-B784-97D3C87E86E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B8C23A-0DC2-43C6-ACA4-F6422450FE6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="796" firstSheet="7" activeTab="14" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="132">
   <si>
     <t>node</t>
   </si>
@@ -454,6 +454,9 @@
   </si>
   <si>
     <t>inflow</t>
+  </si>
+  <si>
+    <t>deviation_penalty</t>
   </si>
 </sst>
 </file>
@@ -5897,13 +5900,13 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{076D8023-527F-4386-8A27-2EF08439356E}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>126</v>
       </c>
@@ -5921,6 +5924,9 @@
       </c>
       <c r="F1" t="s">
         <v>130</v>
+      </c>
+      <c r="G1" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
